--- a/apps/backend/tests/fixtures/normalization_bundle_minimal.xlsx
+++ b/apps/backend/tests/fixtures/normalization_bundle_minimal.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>{"normalized":{"market":["SE"],"alias_types_present":["plate","vin","model_name"],"legal_manufacturer":"VOLVO CAR CORPORATION","vin_manufacturing_entity":"Volvo","manufacturer":"Volvo","manufacturer_role":"vehicle_manufacturer","builder_converter_names":[],"manufacturer_evidence":["manufacturer"],"model_family_candidate":true,"power_kw":145,"power_source_unit":"kw","displacement_cc":1969,"displacement_source_unit":"ccm","transmission_type":"automatic","bodywork_registry_code":"AC","bodywork_registry_label_sv":"Stationsvagn (kombivagn)","bodywork_form":"estate","bodywork_source":"registry"},"candidates":{"model_family":"V60"},"candidate_rule_ids":[],"confidence":0.55,"pipeline_version":"normalization-pipeline-v5","decision_trace":[{"sequence":1,"transformer_id":"ts.initialize","target":"normalized","field":"alias_types_present","rule_ids":["SYS-TS-INIT"],"before":null,"after":["plate","vin","model_name"],"confidence_effect":0.0},{"sequence":2,"transformer_id":"ts.initialize","target":"normalized","field":"market","rule_ids":["SYS-TS-INIT"],"before":null,"after":["SE"],"confidence_effect":0.0},{"sequence":3,"transformer_id":"ts.manufacturer","target":"normalized","field":"builder_converter_names","rule_ids":["MFR-102"],"before":"VOLVO CAR CORPORATION","after":[],"confidence_effect":0.2},{"sequence":4,"transformer_id":"ts.manufacturer","target":"normalized","field":"legal_manufacturer","rule_ids":["MFR-102"],"before":"VOLVO CAR CORPORATION","after":"VOLVO CAR CORPORATION","confidence_effect":0.2},{"sequence":5,"transformer_id":"ts.manufacturer","target":"normalized","field":"manufacturer","rule_ids":["MFR-102"],"before":"VOLVO CAR CORPORATION","after":"Volvo","confidence_effect":0.2},{"sequence":6,"transformer_id":"ts.manufacturer","target":"normalized","field":"manufacturer_evidence","rule_ids":["MFR-102"],"before":"VOLVO CAR CORPORATION","after":["manufacturer"],"confidence_effect":0.2},{"sequence":7,"transformer_id":"ts.manufacturer","target":"normalized","field":"manufacturer_role","rule_ids":["MFR-102"],"before":"VOLVO CAR CORPORATION","after":"vehicle_manufacturer","confidence_effect":0.2},{"sequence":8,"transformer_id":"ts.manufacturer","target":"normalized","field":"vin_manufacturing_entity","rule_ids":["MFR-102"],"before":"VOLVO CAR CORPORATION","after":"Volvo","confidence_effect":0.2},{"sequence":9,"transformer_id":"ts.model-family","target":"normalized","field":"model_family_candidate","rule_ids":["MODEL-CANDIDATE-V1"],"before":"V60","after":true,"confidence_effect":0.1},{"sequence":10,"transformer_id":"ts.model-family","target":"candidate","field":"model_family","rule_ids":["MODEL-CANDIDATE-V1"],"before":"V60","after":"V60","confidence_effect":0.05},{"sequence":11,"transformer_id":"ts.engine-measurements","target":"normalized","field":"displacement_cc","rule_ids":["UNIT-POWER-KW-V1","UNIT-DISPLACEMENT-CCM-V1"],"before":{"kw":145,"ccm":1969},"after":1969,"confidence_effect":0.1},{"sequence":12,"transformer_id":"ts.engine-measurements","target":"normalized","field":"displacement_source_unit","rule_ids":["UNIT-POWER-KW-V1","UNIT-DISPLACEMENT-CCM-V1"],"before":{"kw":145,"ccm":1969},"after":"ccm","confidence_effect":0.1},{"sequence":13,"transformer_id":"ts.engine-measurements","target":"normalized","field":"power_kw","rule_ids":["UNIT-POWER-KW-V1","UNIT-DISPLACEMENT-CCM-V1"],"before":{"kw":145,"ccm":1969},"after":145,"confidence_effect":0.1},{"sequence":14,"transformer_id":"ts.engine-measurements","target":"normalized","field":"power_source_unit","rule_ids":["UNIT-POWER-KW-V1","UNIT-DISPLACEMENT-CCM-V1"],"before":{"kw":145,"ccm":1969},"after":"kw","confidence_effect":0.1},{"sequence":15,"transformer_id":"ts.transmission","target":"normalized","field":"transmission_type","rule_ids":["TRN-008"],"before":{"gearbox":"Z","model":"V60"},"after":"automatic","confidence_effect":0.1},{"sequence":16,"transformer_id":"ts.bodywork","target":"normalized","field":"bodywork_form","rule_ids":["BDY-110"],"before":{"body_code":"AC","eu_category":"M1","model":"V60"},"after":"estate","confidence_effect":0.1},{"sequence":17,"transformer_id":"ts.bodywork","target":"normalized","field":"bodywork_registry_code","rule_ids":["BDY-110"],"before":{"body_code":"AC","eu_category":"M1","model":"V60"},"after":"AC","confidence_effect":0.1},{"sequence":18,"transformer_id":"ts.bodywork","target":"normalized","field":"bodywork_registry_label_sv","rule_ids":["BDY-110"],"before":{"body_code":"AC","eu_category":"M1","model":"V60"},"after":"Stationsvagn (kombivagn)","confidence_effect":0.1},{"sequence":19,"transformer_id":"ts.bodywork","target":"normalized","field":"bodywork_source","rule_ids":["BDY-110"],"before":{"body_code":"AC","eu_category":"M1","model":"V60"},"after":"registry","confidence_effect":0.1},{"sequence":20,"transformer_id":"ts.fuel","target":"review","field":"review_reason","rule_ids":["FUEL-LOOKUP-V1"],"before":{"fuel1":"BENSIN","model":"V60"},"after":"fuel1_code_unknown","confidence_effect":-0.2}],"rule_matches":[{"rule_set_version":"ts-review-fixture-v1","rule_id":"TRN-008","decision":"accepted","source_field":"gearbox","source_term":"Z","target_field":"transmission_type","canonical_value":"automatic"},{"rule_set_version":"ts-review-fixture-v1","rule_id":"BDY-110","decision":"accepted","source_field":"body_code","source_term":"AC","target_field":"bodywork_form","canonical_value":"estate"}]}</t>
+          <t>{"normalized":{"market":["SE"],"alias_types_present":["plate","vin","model_name"],"legal_manufacturer":"VOLVO CAR CORPORATION","vin_manufacturing_entity":"Volvo","manufacturer":"Volvo","manufacturer_role":"vehicle_manufacturer","builder_converter_names":[],"manufacturer_evidence":["manufacturer"],"model_family_candidate":true,"power_kw":145,"power_source_unit":"kw","displacement_cc":1969,"displacement_source_unit":"ccm","transmission_type":"automatic","bodywork_registry_code":"AC","bodywork_registry_label_sv":"Stationsvagn (kombivagn)","bodywork_form":"estate","bodywork_source":"registry","vehicle_scope":"passenger"},"candidates":{"model_family":"V60"},"candidate_rule_ids":[],"confidence":0.55,"pipeline_version":"normalization-pipeline-v5","decision_trace":[{"sequence":1,"transformer_id":"ts.initialize","target":"normalized","field":"alias_types_present","rule_ids":["SYS-TS-INIT"],"before":null,"after":["plate","vin","model_name"],"confidence_effect":0.0},{"sequence":2,"transformer_id":"ts.initialize","target":"normalized","field":"market","rule_ids":["SYS-TS-INIT"],"before":null,"after":["SE"],"confidence_effect":0.0},{"sequence":3,"transformer_id":"ts.manufacturer","target":"normalized","field":"builder_converter_names","rule_ids":["MFR-102"],"before":"VOLVO CAR CORPORATION","after":[],"confidence_effect":0.2},{"sequence":4,"transformer_id":"ts.manufacturer","target":"normalized","field":"legal_manufacturer","rule_ids":["MFR-102"],"before":"VOLVO CAR CORPORATION","after":"VOLVO CAR CORPORATION","confidence_effect":0.2},{"sequence":5,"transformer_id":"ts.manufacturer","target":"normalized","field":"manufacturer","rule_ids":["MFR-102"],"before":"VOLVO CAR CORPORATION","after":"Volvo","confidence_effect":0.2},{"sequence":6,"transformer_id":"ts.manufacturer","target":"normalized","field":"manufacturer_evidence","rule_ids":["MFR-102"],"before":"VOLVO CAR CORPORATION","after":["manufacturer"],"confidence_effect":0.2},{"sequence":7,"transformer_id":"ts.manufacturer","target":"normalized","field":"manufacturer_role","rule_ids":["MFR-102"],"before":"VOLVO CAR CORPORATION","after":"vehicle_manufacturer","confidence_effect":0.2},{"sequence":8,"transformer_id":"ts.manufacturer","target":"normalized","field":"vin_manufacturing_entity","rule_ids":["MFR-102"],"before":"VOLVO CAR CORPORATION","after":"Volvo","confidence_effect":0.2},{"sequence":9,"transformer_id":"ts.model-family","target":"normalized","field":"model_family_candidate","rule_ids":["MODEL-CANDIDATE-V1"],"before":"V60","after":true,"confidence_effect":0.1},{"sequence":10,"transformer_id":"ts.model-family","target":"candidate","field":"model_family","rule_ids":["MODEL-CANDIDATE-V1"],"before":"V60","after":"V60","confidence_effect":0.05},{"sequence":11,"transformer_id":"ts.engine-measurements","target":"normalized","field":"displacement_cc","rule_ids":["UNIT-POWER-KW-V1","UNIT-DISPLACEMENT-CCM-V1"],"before":{"kw":145,"ccm":1969},"after":1969,"confidence_effect":0.1},{"sequence":12,"transformer_id":"ts.engine-measurements","target":"normalized","field":"displacement_source_unit","rule_ids":["UNIT-POWER-KW-V1","UNIT-DISPLACEMENT-CCM-V1"],"before":{"kw":145,"ccm":1969},"after":"ccm","confidence_effect":0.1},{"sequence":13,"transformer_id":"ts.engine-measurements","target":"normalized","field":"power_kw","rule_ids":["UNIT-POWER-KW-V1","UNIT-DISPLACEMENT-CCM-V1"],"before":{"kw":145,"ccm":1969},"after":145,"confidence_effect":0.1},{"sequence":14,"transformer_id":"ts.engine-measurements","target":"normalized","field":"power_source_unit","rule_ids":["UNIT-POWER-KW-V1","UNIT-DISPLACEMENT-CCM-V1"],"before":{"kw":145,"ccm":1969},"after":"kw","confidence_effect":0.1},{"sequence":15,"transformer_id":"ts.transmission","target":"normalized","field":"transmission_type","rule_ids":["TRN-008"],"before":{"gearbox":"Z","model":"V60"},"after":"automatic","confidence_effect":0.1},{"sequence":16,"transformer_id":"ts.bodywork","target":"normalized","field":"bodywork_form","rule_ids":["BDY-110"],"before":{"body_code":"AC","eu_category":"M1","model":"V60"},"after":"estate","confidence_effect":0.1},{"sequence":17,"transformer_id":"ts.bodywork","target":"normalized","field":"bodywork_registry_code","rule_ids":["BDY-110"],"before":{"body_code":"AC","eu_category":"M1","model":"V60"},"after":"AC","confidence_effect":0.1},{"sequence":18,"transformer_id":"ts.bodywork","target":"normalized","field":"bodywork_registry_label_sv","rule_ids":["BDY-110"],"before":{"body_code":"AC","eu_category":"M1","model":"V60"},"after":"Stationsvagn (kombivagn)","confidence_effect":0.1},{"sequence":19,"transformer_id":"ts.bodywork","target":"normalized","field":"bodywork_source","rule_ids":["BDY-110"],"before":{"body_code":"AC","eu_category":"M1","model":"V60"},"after":"registry","confidence_effect":0.1},{"sequence":20,"transformer_id":"ts.fuel","target":"review","field":"review_reason","rule_ids":["FUEL-LOOKUP-V1"],"before":{"fuel1":"BENSIN","model":"V60"},"after":"fuel1_code_unknown","confidence_effect":-0.2},{"sequence":21,"transformer_id":"ts.vehicle-scope","target":"normalized","field":"vehicle_scope","rule_ids":["VEHICLE-SCOPE-V1"],"before":"M1","after":"passenger","confidence_effect":0.0}],"rule_matches":[{"rule_set_version":"ts-review-fixture-v1","rule_id":"TRN-008","decision":"accepted","source_field":"gearbox","source_term":"Z","target_field":"transmission_type","canonical_value":"automatic"},{"rule_set_version":"ts-review-fixture-v1","rule_id":"BDY-110","decision":"accepted","source_field":"body_code","source_term":"AC","target_field":"bodywork_form","canonical_value":"estate"}]}</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
